--- a/artfynd/S 604-2024 artfynd.xlsx
+++ b/artfynd/S 604-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,6 +1113,117 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135202611</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100241</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222654</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunag</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhynchospora fusca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) W. T. Aiton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>IGLASJÖN MOT SSO, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>371038</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6294526</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvibille</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Rännil gungfly</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 604-2024 artfynd.xlsx
+++ b/artfynd/S 604-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128516025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80677444</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108537207</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89655454</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,8 +1248,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135202611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 604-2024 artfynd.xlsx
+++ b/artfynd/S 604-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>135202611</v>
       </c>
       <c r="B6" t="n">
-        <v>100241</v>
+        <v>100288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 604-2024 artfynd.xlsx
+++ b/artfynd/S 604-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>135202611</v>
       </c>
       <c r="B6" t="n">
-        <v>100288</v>
+        <v>100315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 604-2024 artfynd.xlsx
+++ b/artfynd/S 604-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,6 +1135,122 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89655454</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135202611</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100320</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222654</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunag</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhynchospora fusca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) W. T. Aiton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>IGLASJÖN MOT SSO, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>371038</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6294526</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvibille</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Rännil gungfly</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135202611</t>
         </is>
       </c>
     </row>
@@ -1144,6 +1260,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 604-2024 artfynd.xlsx
+++ b/artfynd/S 604-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>135202611</v>
       </c>
       <c r="B6" t="n">
-        <v>100320</v>
+        <v>100322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
